--- a/Excel/11_Wastewater_WIP_v01.xlsx
+++ b/Excel/11_Wastewater_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB31BC6-4C1B-42FD-B735-94EE915718CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A355C341-4380-4EEB-A604-9F133A20C0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="75" windowWidth="30690" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="111" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="124" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -184,37 +187,52 @@
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Title">_xlfn.LAMBDA("The direct nitrous oxide EF from the organic fertiliser when applied to soils")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Unit">_xlfn.LAMBDA("(kg NH3-N + NOx-N)/kg N")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Variation">_xlfn.LAMBDA(("VARIATION FROM SOURCE DATA: Added extra 'Basis' column with simplified naming to assis with lookups in equations"))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain(_xlpm.LivestockClass, _xlpm.MovementDate) * CommonLivestock_InputFunctions.LivestockMovement_DaysMovementToMonthEnd(_xlpm.MovementDate), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain(_xlpm.LivestockClass, _xlpm.MovementDate) * CommonLivestock_InputFunctions.LivestockMovement_DaysMovementToMonthEnd(_xlpm.MovementDate), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month, '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, EOMONTH(_xlpm.Month, -1) + 1))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, EOMONTH(_xlpm.Month, -1) + 1))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month,_xlpm.HeadAtStartOfMonth, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStartOfMonth) * '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead(_xlpm.LivestockClass, _xlpm.Month))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month,_xlpm.HeadAtStartOfMonth, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStartOfMonth) * [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead(_xlpm.LivestockClass, _xlpm.Month))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMovementDateTotal" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.Head, '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate) * _xlpm.Head)</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMovementDateTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.Head, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate) * _xlpm.Head)</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * [0]!CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, '11.1.3-4 Wastewater N2O'!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
+    <definedName name="Step1">#REF!</definedName>
+    <definedName name="Step2">#REF!</definedName>
+    <definedName name="Step3">#REF!</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment">_xlfn.LAMBDA(_xlpm.W_t,_xlpm.COD_in,_xlpm.F_sludge,_xlpm.COD_out,_xlpm.CF_ww_t,_xlpm.EF_ww,_xlpm.F_removed,_xlpm.CF_sludge_t,_xlpm.EF_sludge,_xlpm.Q_cap,_xlpm.Q_flared,_xlpm.Q_out,_xlpm.EC_flared,_xlpm.EF_flaredCH4, (1 / 1000) * ((_xlpm.W_t * (_xlpm.COD_in * (1 - _xlpm.F_sludge) - _xlpm.COD_out) * _xlpm.CF_ww_t * _xlpm.EF_ww) + (_xlpm.W_t * (_xlpm.COD_in * (_xlpm.F_sludge - _xlpm.F_removed)) * _xlpm.CF_sludge_t * _xlpm.EF_sludge) - (6.784 * 10 ^ -4 * (_xlpm.Q_cap + _xlpm.Q_flared + _xlpm.Q_out)) + (_xlpm.Q_flared * (_xlpm.EC_flared * _xlpm.EF_flaredCH4))))</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"W_t","quantity of wastewater treated at facility type t","m3","Input";"COD_in","average inlet Chemical Oxygen Demand concentration of wastewater","kg COD/m3","Input";"F_sludge","fraction of COD removed from wastewater as sludge","fraction","Input";"COD_out","average outlet COD concentration of wastewater","kg COD/m3","Input";"CF_ww_t","methane correction factor for facility type t used to treat wastewater","fraction","Constant";"EF_ww","methane emission factor for wastewater","kg CH4/kg COD","Constant";"F_removed","fraction of COD removed from the wastewater treatment facility and transferred elsewhere","fraction","Input";"CF_sludge_t","methane correction factor for facility type t used to treat sludge","fraction","Constant";"EF_sludge","methane emission factor for sludge","kg CH4/kg COD","Constant";"Q_cap","quantity of methane in sludge biogas captured for combustion","m3 CH4","Input";"Q_flared","quantity of methane in sludge biogas flared by the treatment facility","m3 CH4","Input";"Q_out","quantity of methane in sludge biogas transferred out of the treatment facility","m3 CH4","Input";"EC_flared","energy content factor of methane in sludge biogas flared","GJ/m3","Constant";"EF_flaredCH4","methane emission factor for sludge biogas flared","kg CH4/GJ","Constant";"t","treatment facility type","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_LatexEquation">_xlfn.LAMBDA(_xlfn._LONGTEXT("E_{CH4}=\frac{1}{1000}\times\left{\left{W_t\times\left[COD_{in}\times(1-F_{sludge})-COD_{out}\right]\times CF_{ww,t}\times EF_{ww}\right}+\left{W_t\times\left[COD_{in}\times(F_{sludge}-F_{removed})\right]\times CF_{sludge,t}\times EF_{sludge}\right}-\left","{6.784\times 10^{-4}\times \left[ Q_{cap}+Q_{flared}+Q_{out}\right]\right}+\left{Q_{flared}\times \left[ EC_{flared}\times EF_{flared,CH4}\right]\right}\right}"))</definedName>
@@ -1933,176 +1951,6 @@
   <dxfs count="71">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2962,6 +2810,176 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5223,6 +5241,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5306,7 +5344,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F8066D7D-5B7A-4C2D-96C5-0B642AEDBDD8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{AFAB6A22-121F-4A50-9152-A8E580122815}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5314,16 +5352,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFC2CD32-0D6A-477F-9AB9-8CC735000875}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{F2A7B006-3B9B-490B-A956-7F904A9BC1A0}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F05498-A494-40EC-A370-E31F9319F6E9}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{A3178854-1904-46B6-9601-FBCC390F839C}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0FEB24E7-52AA-4E09-8CAD-E3593BA1850C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{D21F920E-74C3-43C6-8E18-6CFD69944EC3}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9588CB4-A6E3-43EF-86F2-28512F6C0466}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{39CF9EA2-C9B6-41EC-AC58-E1943DCC6E03}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5332,16 +5370,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{371EB3B0-E5DE-49F4-9F8F-370B9594177E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{DB5808CD-4C52-49C0-8D9C-DDD27E7ABF86}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EC0469C-3AAC-4C25-8B45-E899791ECD1F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{4B17C9DE-741E-4223-8B98-9DA237A2543C}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D8738CB7-C0A6-466E-AD54-75590BF18BAC}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{9AE87DF0-C92B-4748-9688-790D35C88B2F}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5350,16 +5388,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{8320C659-C167-4CAA-9C06-854A612436E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F67892C5-921B-4BA8-8C3E-941A4EBD5456}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2CBE0C09-88F8-4FC0-91F9-37AD76A1AEAA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{F1C79171-18D4-4538-B8B5-4035B9BDADE4}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{390BA082-D34B-4509-BBAD-72ABE42C4B39}" name="Data score">
+    <tableColumn id="2" xr3:uid="{F4879EF9-AFF2-4FBB-8AC4-10E9136CB398}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5368,16 +5406,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{D7EAD11A-DC1E-416A-A0F3-2127BEE727A4}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{B1B8ACAC-A09F-4E48-8944-728EA0065A24}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0B2F492-E516-47ED-A029-67FEF667A678}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{AC686EA2-8D9A-4D6D-A8A8-062FB3B515CC}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{51E6CA6F-68DC-47AB-A1BB-C75D3CA8FA3B}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{1FCEBDA5-65F4-46B1-B370-C11FB49932FA}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5386,7 +5424,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{BE2E746E-A542-4963-9138-4CB3534F691E}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{90C0F7AC-0F98-4652-98CC-95BA4A16C131}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5395,19 +5433,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10155645-FDE5-446A-BDDD-C71CD77DD825}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{DC10BB70-498C-4145-BAE7-7A04D5280125}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A33C56B8-DAE9-434B-8228-CD6E219067F7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{9A35A152-BB7C-4846-9F6E-3E9C99E73442}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{415F2F98-1C0C-4F1B-A357-E4F0898F9DA1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{748EC603-7F46-49E5-A98E-535FE8846206}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{364F973B-700F-4051-9AE8-A5B5A5144B24}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{A56CD644-C6AA-445E-9F25-4B23A92A9B64}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B401083-C682-49B6-9293-290F6E0CCE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{CCAB1984-3AF3-43D3-81A5-8CE900C98160}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5416,16 +5454,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{F2CB8BB6-7664-477A-B6EF-EAA92A00C8A0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4165A077-B250-4DEE-B369-59E4E7679902}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0CAEDF1E-5A86-4C59-ADB4-2A63E7ABD4DD}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{F2C9E476-6A55-47D9-B3E7-C67EA63535FA}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{57851871-7E08-4269-B67C-A96E5A947487}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{88DAA629-0590-41E1-A2CC-610CF9FDB97C}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5434,16 +5472,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{BFE0DDAE-EACA-4433-A3E7-753CE50EADFD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{87CE216A-9BD9-485A-9EB8-B9E0DFCC2C93}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{04E57D99-757F-4374-BB84-42339A5C3083}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{AF9CBDC1-27EF-4EED-B8DF-92F594F394C9}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92543612-DE1F-4C45-B1F2-46B34452C302}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F1AF672B-1B1A-422D-A6B3-621D6214B60E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5452,16 +5490,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{31E1F417-A09B-41DA-9456-3458FDF04264}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{DEDBE9B8-7638-405B-BBEA-28F4A90E5FDC}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C54F0C5-3505-4964-A85B-6C95900D28A5}" name="Month">
+    <tableColumn id="1" xr3:uid="{F56D4BDC-1A8D-48FE-B31E-DE67F81E1C52}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE5E22FE-C43A-4172-9EDB-6FE00B1DF854}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{84A8C1F6-0D04-4FAE-AC8C-5DCE94CD2667}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5470,7 +5508,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{AF70AA04-1AD5-4DF8-9CC4-5F92B5EE2A0A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{FB2C0D77-D19C-4F62-8E5B-44E9019BF690}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5490,52 +5528,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FD606263-AC8F-4B13-96E2-C9CA0ECFC2B3}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{F0787CE1-8BC3-48A0-BD72-4D31FF2981AB}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{328E4735-CE75-4070-9C88-AE6AC281FA52}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{236F7AC5-AA7A-4B5B-A91D-B3234A850B1F}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAAA9F18-86A5-4F62-9B13-8EC468FD3268}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{C188DBCE-83A9-4948-B739-6D8CFA8FB1F1}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16CDDAC7-40E8-4B7E-A5A7-534574EF9960}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{7F0A7CCE-9091-445B-A615-A547A51F5200}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BE7531C-242C-4F06-B612-2455D4071B48}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{F45FD72F-73B7-4580-B927-C93DC98F52E5}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AA6EA91-67D5-4225-8E66-D79949E45C79}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{C72DB022-C4D0-41C7-A672-C4F576EDC815}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A682CC91-6B5E-45D1-857C-0228079BCC7C}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{98BE1154-A30B-4B37-8D42-1FCB8196ADFF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{516A42DC-F452-4685-9EE1-8DB5323E888F}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{FE6F67A9-BD27-47E8-B501-A2D2DDFAFD2B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3E59565B-237D-4BF7-8514-8C00EE69787F}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1612D188-6F19-4A62-9F7B-984763732FCD}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B94C989A-1174-49BC-8E63-5C88C372C925}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{F2B629FE-D9AC-43BB-8712-0244FAFED160}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4E416B5A-6B9A-4444-8C96-0603C11DC870}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{AEB1AAB3-C1F7-4609-811C-C8F71F27BEA7}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2302252A-7FB0-4046-9B12-B1CD2F1BBED4}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{30CD3C79-0D8E-4E7F-87FD-8F4EA6115707}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50CED419-50AF-49B3-8F42-E496D5B781AB}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{B6966C78-6D1B-4D36-AF62-930896F91722}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FACDE6F8-8A2F-4040-8D12-2E35D0831482}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{319A832A-BD0E-4DCC-BA3B-3FE865BD158B}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2134A83A-1EB7-471E-ADAA-05ADE14C7593}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{1A0A5924-316D-4A5B-BC7C-60065B83EB70}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C3199CA-00F6-4D2D-9A1A-14E5576B6B3A}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{41772124-674F-460B-8395-C3AE2FD9C178}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5544,16 +5582,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
-  <autoFilter ref="D257:E259" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{79E744CC-76BA-4DD4-AC67-44F809197B90}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6441941C-5801-414B-9EFC-BFCD02E9AABA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{9399ABC9-646D-4864-8875-225CB798A120}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFFF76A7-AEC2-426D-9FB9-7DCEAE399701}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{828CCD4A-4F4D-4667-8FE5-C00753040270}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5580,20 +5618,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3AE6144E-A1E7-4518-B032-EF188F35C422}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BAB9D8D8-A94C-4765-A2F4-FBF3EB858A25}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A67EF497-7B1B-4776-9D83-A8AD1BEAF517}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{171512E4-DD77-45F5-A7DC-7F756E38E58B}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E9614A8-2F7E-4491-9C0D-E14664D3CBD5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{67A2E349-9D96-4192-BF1C-973FE556FADB}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48FCC7EC-93CF-4022-930C-DFF884BE9C3A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{6C9B778A-6BC0-4CBC-92FC-621305E6382A}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5602,12 +5640,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A98080EA-F2FB-4179-A336-59EF5AF50E8F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D149E782-62CC-4024-A8A1-E5EA1E498D2A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E44BE92-8969-4CB0-B814-3C00C2C18F3C}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{9D56D53A-6694-4B57-A02F-8E9551CB7A14}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5616,16 +5654,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{3B270221-00F4-4B48-BE2F-1F9DCAB7874A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{BDA15D44-60E0-4864-879A-DD3FCF3315EE}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D82C5D5A-F88F-46E7-868F-025402490369}" name="Gas">
+    <tableColumn id="1" xr3:uid="{29D0E979-289C-49F4-93D3-6124A7F51BE5}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6DC661F8-0615-4FB7-8AE2-83962657C55A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{F1769B4A-4D35-4F1E-B9DA-F65441424CD9}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5634,7 +5672,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{79E591EE-C4BF-4FA2-8F75-39DA84C25602}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{F352728F-1C63-4F70-B975-4EF1CA2C819D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5643,19 +5681,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BABC03E3-165B-407A-BF04-28738E72D28A}" name="Gas">
+    <tableColumn id="1" xr3:uid="{4AD24F5B-C1DA-4F22-BB17-81A6F8D71410}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF0196FE-D2CF-4F66-8847-9CE3DB549E9B}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{B50E9557-5672-4944-AC8B-E65E187DE052}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71C50FB6-28B8-4C5F-B7F7-F9E98423215B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{85EF82D1-0A91-4FC0-96CC-52E8DE88242E}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E60D175-C714-4272-922B-6384C81A6A4A}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{CC9DBC6F-DAFE-493B-A2AD-0B39C1BB80DB}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77C6E5B1-2CB1-4714-9B60-3FC1F2C784D3}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{B37F38D1-8FCD-4B3A-A678-FA02F0A28A61}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5664,7 +5702,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EB24DAD-7938-4A28-8102-A92DD6232701}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0570EA12-3286-4560-9BE6-60258611BC9D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5684,52 +5722,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7C646E3D-156E-438B-9E75-102B5E96E255}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{6ED0CF1D-7CD9-4066-8EE4-25FE923E5D3B}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F6652C3-1BDE-4F33-9D5E-1BA7F24CFE1E}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{CF963462-2F2C-4BF6-A892-086541529F20}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{68D3A033-0C56-472E-A3CF-B482905871CF}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1B3F3876-9D6F-447A-A423-66E21AC0558A}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{18D7CFC5-1F89-47C0-AF12-0FD6A80AD2C8}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{A4802F3E-DC20-40F1-AC5A-D182C68519BB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{694DED4D-19CA-49A7-A7A4-ED3CD36E0BA2}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{1F7F9556-3126-439E-875C-D76E463F8036}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BE47AD00-59A1-4916-A3FF-4E905492D142}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DBB23AF3-C817-42CE-BE89-ADDA8D904773}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CD0BB0E-B9A0-4065-920B-F859089361EB}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{60216B5C-783A-4916-AACF-4280FF3BECAD}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AD474F5-6F0E-4F15-87EA-A3E86BD8CD84}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{1FE05885-DAC3-47B8-BEB3-6920E3033122}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4132B96D-08DF-47B8-9134-F88DA6CBA26A}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{2B644226-778B-401E-99C4-CEB1DE3EDAE1}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{799D2CC4-68A8-4F6B-B5E8-BA9B134CD629}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{B73B8CF5-08DF-4843-B82E-B9FB1813470C}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF3C7CFE-CC8F-4407-9CD2-DB7BCF735828}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{2516891E-4C4A-426D-8B84-5149409BFCBC}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9CB12B6D-F283-41CE-A0AC-7DA70F3FEA35}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{189C1E5A-6304-4676-A9EB-8B293F4544B2}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{DE6B8D57-DEA5-4CDB-BEA5-6794B3B8B4C1}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{14B9E9DB-0BCC-48C2-8CCA-57C75DB45D61}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F1C5507D-FFFD-4456-AAE0-9309987F0339}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{67D82299-FF27-4038-A32D-781A02A531ED}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB91B1DF-4B57-426B-BF6A-71715747D3B2}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FB2C0315-064C-437A-86D7-3E8FA9F4822B}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7674CAA3-6E67-48AA-BF62-AECA84F01CB9}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{378C37E5-D887-4B5C-9001-232EF0A792B4}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5738,16 +5776,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{3FAC77B2-7BB0-4B78-B387-3E2D5CA67215}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4D2F7A40-370B-4A1A-BB7E-6930F4763E13}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9DF69629-1C76-40A4-BBA1-FB28BF754268}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{44AAB7B6-31A0-4522-84AE-3428F2D4D02F}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99A9C0E3-7924-426C-A581-5C219452362E}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{8619F0C7-D005-4F89-B453-E75937AA076E}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5756,7 +5794,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{AE4202F8-BB52-48CE-B368-8D0A44A67525}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{DA18547E-C2B9-4253-9B23-ECFAF5D3F0C4}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5764,16 +5802,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4BD1B715-E9FF-4B2E-A162-3DD06FA33AAE}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{05952A61-6A28-4826-9977-99686E3CA96D}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDEC609-65F3-40EC-B489-B99CC8E44680}" name="MAT">
+    <tableColumn id="2" xr3:uid="{F49ABE84-00CE-4251-9431-9E6E70A546AC}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25C140A7-4F53-46DB-A6E5-3FFA5FE81DD6}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{0323FC01-6733-41DC-9E79-98C1FED01EC8}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2D4126F-3B56-4A19-AD7E-FA0C2ECA0D87}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{F9992E54-F3A7-462B-BC56-E5BA0C72765F}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7804,87 +7842,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D39:H43">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F148:F149">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F160:F161">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F172:F173">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="12" priority="94" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="94" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F265:F266">
-    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270:F271">
-    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="9" priority="86" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="86" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F299:F300">
-    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F304:F305">
-    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65:I69">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73 I132">
-    <cfRule type="cellIs" dxfId="5" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="75" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I86">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90:I93">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I97:I101">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 I51:I52 H53:H55 I54 I56:I58 I60:I61 I212 I218 E220:G220">
-    <cfRule type="cellIs" dxfId="1" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="80" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J37 I45 F136:F137">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9755,7 +9793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C96C07E-3BBC-40AD-9550-B73B24462357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB47BE6-A391-432F-B8D2-A68CD0E0E20E}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11159,31 +11197,31 @@
       </c>
       <c r="T97" s="26"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="30" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="30" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="30" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="30" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="30" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="30" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="30"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="30"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="str" cm="1">
@@ -13962,7 +14000,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIAAnAEYAcgB5ACcAIAB0AG8AIAAnAEQAcgB5ACcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAPgAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMgAwADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAZQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAVAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBQACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAARQBUACAAPQAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZQB2AGEAcABvAHQAcgBhAG4AcwBwAGkAcgBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAATQBBAFQAIABtAGkAbgAgAGEAbgBkACAATQBBAFQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAIABmAHIAbwBtACAAcgBlAGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAGQAYQB0AGEALgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBlAGQAaQBhAG4AIABBAG4AbgB1AGEAbAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgACgATQBBAFQAKQBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBUAFwAIgAsACAAXAAiAE0AYQB4ACAATQBBAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIgADIANgAgAEMAXAAiACwAIAAyADYALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAXAAiADEANQAgAC0AIAAyADUAIABDAFwAIgAsACAAMQA1ACwAIAAyADUALgA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiIAAxADQAIABDAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQA0AC4AOQA5ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAIABmAHIAbwBtACAAcgBlAGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQAYQB0AGEALgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAFoAbwBuAGUAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIAA+ACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAD4AowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgACcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgACcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQAnACwAIAAnAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAJwAgAGEAbgBkACAAJwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAJwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlACcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcAG4ASQBQAEMAQwA6ACAATgAyAE8AIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABNAEEATgBBAEcARQBEACAAUwBPAEkATABTACwAIABBAE4ARAAgAEMATwAyACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATABJAE0ARQAgAEEATgBEACAAVQBSAEUAQQAgAEEAUABQAEwASQBDAEEAVABJAE8ATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAVwBFAFQAIABmAG8AcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ADoAIABDAGgAYQBwAHQAZQByACAAMQAxADoAIABOADIATwAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAE0AYQBuAGEAZwBlAGQAIABTAG8AaQBsAHMALAAgAGEAbgBkACAAQwBPADIAIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABMAGkAbQBlACAAYQBuAGQAIABVAHIAZQBhACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHAAcgBpAG4AawBsAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQByAGYAYQBjAGUAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFQAYQBiAGwAZQAgAGMAcgBlAGEAdABlAGQAIABiAGEAcwBlAGQAIABvAG4AIABWAEUARQBSAEcAIAB0AGUAeAB0ACAAJwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgAnAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAnACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACcAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBvAG4AdABoAHMAIAB0AG8AIABTAGUAYQBzAG8AbgBzACAATQBhAHAAcABpAG4AZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwBuAHQAaABcACIALAAgAFwAIgBTAGUAYQBzAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBhAG4AdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGIAcgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAcgBjAGgAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcAByAGkAbABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHkAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAdQBuAGUAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAdQBsAHkAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBnAHUAcwB0AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAcAB0AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwBjAHQAbwBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHYAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBlAG0AYgBlAHIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBuAHUAcgBlACAATQBhAG4AYQBnAGUAbQBlAG4AdAAgABMgIABNAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADgALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADIALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQBcACIALAAgAFwAIgBNAEEAVAAgACgAugBDACkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBDAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIATABpAHEAdQBpAGQAIABTAGwAdQByAHIAeQAgACgAdwBpAHQAaABvAHUAdAAgAG4AYQB0AHUAcgBhAGwAIABjAHIAdQBzAHQAKQBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgACgAYgApAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAFMAdABvAHIAYQBnAGUAIAA8ADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIAAnAFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAJwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAHMAZQBwAGEAcgBhAHQAZQAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAAQQBkAGQAZQBkACAAJwBNAEEAVAAgAHIAYQB3ACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBpAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAD4AIAAyAG0AKQBcACIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4ANAA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAEMARgBzAGwAdQBkAGcAZQAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAcwBsAHUAZABnAGUALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAcwBsAHUAZABnAGUALAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGEAZwBlAGQAIABhAGUAcgBvAGIAaQBjACAAdAByAGUAYQB0AG0AZQBuAHQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAG0AYQBuAGEAZwBlAGQAIABhAGUAcgBvAGIAaQBjACAAdAByAGUAYQB0AG0AZQBuAHQAXAAiACwAIAAwAC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAbwByAC8AcgBlAGEAYwB0AG8AcgBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBoAGEAbABsAG8AdwAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAGQiIAAyACAAbQApAFwAIgAsACAAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAPgAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
